--- a/neumatic/data_load/numeracion.xlsx
+++ b/neumatic/data_load/numeracion.xlsx
@@ -1,30 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT_NEUMATIC\neumatic\data_load\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT_NEUMATIC_PGS\neumatic\data_load\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F8FFAD-9EA9-4DC2-96FC-EB7116B74C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E23CAF-0186-4F3A-A586-D1F2018EFFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9C7CDCD7-07CE-4712-B4E8-D68AA005A8A3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{82F2B0B3-B52D-4681-8559-E900541B57A1}"/>
   </bookViews>
   <sheets>
     <sheet name="numeracion" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">numeracion!$A$1:$G$221</definedName>
-    <definedName name="_xlnm.Database">numeracion!$A$1:$G$221</definedName>
+    <definedName name="_xlnm.Database">numeracion!$A$1:$G$241</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="31">
   <si>
     <t>001</t>
   </si>
@@ -98,42 +97,6 @@
     <t>RE</t>
   </si>
   <si>
-    <t>SAN JUSTO</t>
-  </si>
-  <si>
-    <t>SANTA FE</t>
-  </si>
-  <si>
-    <t>PARANA</t>
-  </si>
-  <si>
-    <t>ROSARIO</t>
-  </si>
-  <si>
-    <t>RECREO</t>
-  </si>
-  <si>
-    <t>BAIGORRIA - TRUCK</t>
-  </si>
-  <si>
-    <t>RAFAELA</t>
-  </si>
-  <si>
-    <t>RECONQUISTA</t>
-  </si>
-  <si>
-    <t>BAIGORRIA - RECAPADOS</t>
-  </si>
-  <si>
-    <t>INTERPUERTOS</t>
-  </si>
-  <si>
-    <t>ROSARIO SUD</t>
-  </si>
-  <si>
-    <t>ECOMMERCE</t>
-  </si>
-  <si>
     <t>sucursal</t>
   </si>
   <si>
@@ -159,25 +122,25 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri Light"/>
+      <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -185,7 +148,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -193,7 +156,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -201,35 +164,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -237,7 +200,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -245,14 +208,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -260,14 +223,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -275,7 +238,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -283,24 +246,19 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="MS Shell Dlg 2"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,20 +438,8 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -608,21 +554,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -668,14 +599,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -735,9 +661,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -745,39 +671,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -829,7 +755,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -881,7 +807,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -940,13 +866,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -955,6 +874,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1019,55 +945,74 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{566DD4C6-E472-4C8E-BB58-53751169563F}">
-  <dimension ref="A1:J221"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0FFF690-0665-4CFC-8CA8-412D52A4D68A}">
+  <dimension ref="A1:G241"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1089,14 +1034,8 @@
       <c r="G2" s="1">
         <v>2</v>
       </c>
-      <c r="I2" s="2">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1118,14 +1057,8 @@
       <c r="G3" s="1">
         <v>2</v>
       </c>
-      <c r="I3" s="2">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1147,14 +1080,8 @@
       <c r="G4" s="1">
         <v>2</v>
       </c>
-      <c r="I4" s="2">
-        <v>3</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1176,14 +1103,8 @@
       <c r="G5" s="1">
         <v>2</v>
       </c>
-      <c r="I5" s="2">
-        <v>4</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1205,14 +1126,8 @@
       <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="2">
-        <v>5</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -1234,14 +1149,8 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="I7" s="2">
-        <v>6</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -1252,7 +1161,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="1">
-        <v>3300012154</v>
+        <v>3300016062</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>9</v>
@@ -1263,14 +1172,8 @@
       <c r="G8" s="1">
         <v>2</v>
       </c>
-      <c r="I8" s="2">
-        <v>7</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -1292,14 +1195,8 @@
       <c r="G9" s="1">
         <v>2</v>
       </c>
-      <c r="I9" s="2">
-        <v>8</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -1321,14 +1218,8 @@
       <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="I10" s="2">
-        <v>9</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1350,14 +1241,8 @@
       <c r="G11" s="1">
         <v>2</v>
       </c>
-      <c r="I11" s="2">
-        <v>10</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -1379,14 +1264,8 @@
       <c r="G12" s="1">
         <v>2</v>
       </c>
-      <c r="I12" s="2">
-        <v>11</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -1408,14 +1287,8 @@
       <c r="G13" s="1">
         <v>2</v>
       </c>
-      <c r="I13" s="2">
-        <v>12</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -1438,7 +1311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -1461,7 +1334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -1518,7 +1391,7 @@
         <v>21</v>
       </c>
       <c r="D18" s="1">
-        <v>100001171</v>
+        <v>100001216</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>17</v>
@@ -1541,7 +1414,7 @@
         <v>21</v>
       </c>
       <c r="D19" s="1">
-        <v>100000721</v>
+        <v>100001063</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>17</v>
@@ -1564,7 +1437,7 @@
         <v>21</v>
       </c>
       <c r="D20" s="1">
-        <v>100142512</v>
+        <v>100155366</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>17</v>
@@ -1587,7 +1460,7 @@
         <v>21</v>
       </c>
       <c r="D21" s="1">
-        <v>100076933</v>
+        <v>1900000053</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>17</v>
@@ -1748,7 +1621,7 @@
         <v>22</v>
       </c>
       <c r="D28" s="1">
-        <v>3400003139</v>
+        <v>3400003565</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>9</v>
@@ -1978,7 +1851,7 @@
         <v>22</v>
       </c>
       <c r="D38" s="1">
-        <v>200000881</v>
+        <v>200001014</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>17</v>
@@ -2001,7 +1874,7 @@
         <v>22</v>
       </c>
       <c r="D39" s="1">
-        <v>200000290</v>
+        <v>200000749</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>17</v>
@@ -2024,7 +1897,7 @@
         <v>22</v>
       </c>
       <c r="D40" s="1">
-        <v>200153806</v>
+        <v>200161073</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>17</v>
@@ -2047,7 +1920,7 @@
         <v>22</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>17</v>
@@ -2208,7 +2081,7 @@
         <v>23</v>
       </c>
       <c r="D48" s="1">
-        <v>3500008628</v>
+        <v>3500010844</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>9</v>
@@ -2438,7 +2311,7 @@
         <v>23</v>
       </c>
       <c r="D58" s="1">
-        <v>300000898</v>
+        <v>300001290</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>17</v>
@@ -2461,7 +2334,7 @@
         <v>23</v>
       </c>
       <c r="D59" s="1">
-        <v>300001498</v>
+        <v>300002616</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>17</v>
@@ -2484,7 +2357,7 @@
         <v>23</v>
       </c>
       <c r="D60" s="1">
-        <v>300057388</v>
+        <v>300061159</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>17</v>
@@ -2668,7 +2541,7 @@
         <v>24</v>
       </c>
       <c r="D68" s="1">
-        <v>3600011483</v>
+        <v>3600014085</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>9</v>
@@ -2921,7 +2794,7 @@
         <v>24</v>
       </c>
       <c r="D79" s="1">
-        <v>400000438</v>
+        <v>400000568</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>17</v>
@@ -2944,7 +2817,7 @@
         <v>24</v>
       </c>
       <c r="D80" s="1">
-        <v>400058065</v>
+        <v>400061367</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>17</v>
@@ -2956,7 +2829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>4</v>
       </c>
@@ -2979,487 +2852,467 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
-        <v>5</v>
-      </c>
-      <c r="B82" s="3" t="s">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>5</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C82" s="3">
-        <v>25</v>
-      </c>
-      <c r="D82" s="3">
+      <c r="C82" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D82" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F82" s="3">
-        <v>11</v>
-      </c>
-      <c r="G82" s="3">
-        <v>2</v>
-      </c>
-      <c r="H82" s="4"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="3">
-        <v>5</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C83" s="3">
-        <v>25</v>
-      </c>
-      <c r="D83" s="3">
+      <c r="E82" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" s="1">
+        <v>11</v>
+      </c>
+      <c r="G82" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>5</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C83" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D83" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F83" s="3">
-        <v>11</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2</v>
-      </c>
-      <c r="H83" s="4"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="3">
-        <v>5</v>
-      </c>
-      <c r="B84" s="3" t="s">
+      <c r="E83" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1">
+        <v>11</v>
+      </c>
+      <c r="G83" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>5</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C84" s="3">
-        <v>25</v>
-      </c>
-      <c r="D84" s="3">
+      <c r="C84" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D84" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E84" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F84" s="3">
-        <v>11</v>
-      </c>
-      <c r="G84" s="3">
-        <v>2</v>
-      </c>
-      <c r="H84" s="4"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
-        <v>5</v>
-      </c>
-      <c r="B85" s="3" t="s">
+      <c r="E84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="1">
+        <v>11</v>
+      </c>
+      <c r="G84" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>5</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="3">
-        <v>25</v>
-      </c>
-      <c r="D85" s="3">
+      <c r="C85" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D85" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E85" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F85" s="3">
-        <v>11</v>
-      </c>
-      <c r="G85" s="3">
-        <v>2</v>
-      </c>
-      <c r="H85" s="4"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
-        <v>5</v>
-      </c>
-      <c r="B86" s="3" t="s">
+      <c r="E85" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F85" s="1">
+        <v>11</v>
+      </c>
+      <c r="G85" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>5</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="3">
-        <v>25</v>
-      </c>
-      <c r="D86" s="3">
+      <c r="C86" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D86" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E86" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F86" s="3">
-        <v>11</v>
-      </c>
-      <c r="G86" s="3">
-        <v>2</v>
-      </c>
-      <c r="H86" s="4"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
-        <v>5</v>
-      </c>
-      <c r="B87" s="3" t="s">
+      <c r="E86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F86" s="1">
+        <v>11</v>
+      </c>
+      <c r="G86" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>5</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C87" s="3">
-        <v>25</v>
-      </c>
-      <c r="D87" s="3">
+      <c r="C87" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D87" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" s="3">
-        <v>11</v>
-      </c>
-      <c r="G87" s="3">
-        <v>2</v>
-      </c>
-      <c r="H87" s="4"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
-        <v>5</v>
-      </c>
-      <c r="B88" s="3" t="s">
+      <c r="E87" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F87" s="1">
+        <v>11</v>
+      </c>
+      <c r="G87" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>5</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C88" s="3">
-        <v>25</v>
-      </c>
-      <c r="D88" s="3">
+      <c r="C88" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D88" s="1">
         <v>1400016159</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E88" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F88" s="3">
-        <v>11</v>
-      </c>
-      <c r="G88" s="3">
-        <v>2</v>
-      </c>
-      <c r="H88" s="4"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
-        <v>5</v>
-      </c>
-      <c r="B89" s="3" t="s">
+      <c r="F88" s="1">
+        <v>11</v>
+      </c>
+      <c r="G88" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>5</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C89" s="3">
-        <v>25</v>
-      </c>
-      <c r="D89" s="3">
+      <c r="C89" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D89" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F89" s="3">
-        <v>11</v>
-      </c>
-      <c r="G89" s="3">
-        <v>2</v>
-      </c>
-      <c r="H89" s="4"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
-        <v>5</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C90" s="3">
-        <v>25</v>
-      </c>
-      <c r="D90" s="3">
+      <c r="E89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" s="1">
+        <v>11</v>
+      </c>
+      <c r="G89" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>5</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D90" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E90" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F90" s="3">
-        <v>11</v>
-      </c>
-      <c r="G90" s="3">
-        <v>2</v>
-      </c>
-      <c r="H90" s="4"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
-        <v>5</v>
-      </c>
-      <c r="B91" s="3" t="s">
+      <c r="E90" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" s="1">
+        <v>11</v>
+      </c>
+      <c r="G90" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>5</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C91" s="3">
-        <v>25</v>
-      </c>
-      <c r="D91" s="3">
+      <c r="C91" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D91" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F91" s="3">
-        <v>11</v>
-      </c>
-      <c r="G91" s="3">
-        <v>2</v>
-      </c>
-      <c r="H91" s="4"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
-        <v>5</v>
-      </c>
-      <c r="B92" s="3" t="s">
+      <c r="E91" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F91" s="1">
+        <v>11</v>
+      </c>
+      <c r="G91" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>5</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C92" s="3">
-        <v>25</v>
-      </c>
-      <c r="D92" s="3">
+      <c r="C92" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D92" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E92" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F92" s="3">
-        <v>11</v>
-      </c>
-      <c r="G92" s="3">
-        <v>2</v>
-      </c>
-      <c r="H92" s="4"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="3">
-        <v>5</v>
-      </c>
-      <c r="B93" s="3" t="s">
+      <c r="E92" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F92" s="1">
+        <v>11</v>
+      </c>
+      <c r="G92" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>5</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C93" s="3">
-        <v>25</v>
-      </c>
-      <c r="D93" s="3">
+      <c r="C93" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D93" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E93" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F93" s="3">
-        <v>11</v>
-      </c>
-      <c r="G93" s="3">
-        <v>2</v>
-      </c>
-      <c r="H93" s="4"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="3">
-        <v>5</v>
-      </c>
-      <c r="B94" s="3" t="s">
+      <c r="E93" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F93" s="1">
+        <v>11</v>
+      </c>
+      <c r="G93" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>5</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C94" s="3">
-        <v>25</v>
-      </c>
-      <c r="D94" s="3">
+      <c r="C94" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D94" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3">
-        <v>11</v>
-      </c>
-      <c r="G94" s="3">
-        <v>2</v>
-      </c>
-      <c r="H94" s="4"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="3">
-        <v>5</v>
-      </c>
-      <c r="B95" s="3" t="s">
+      <c r="E94" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="1">
+        <v>11</v>
+      </c>
+      <c r="G94" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>5</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C95" s="3">
-        <v>25</v>
-      </c>
-      <c r="D95" s="3">
+      <c r="C95" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D95" s="1">
         <v>500000000</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F95" s="3">
-        <v>11</v>
-      </c>
-      <c r="G95" s="3">
-        <v>2</v>
-      </c>
-      <c r="H95" s="4"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="3">
-        <v>5</v>
-      </c>
-      <c r="B96" s="3" t="s">
+      <c r="E95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" s="1">
+        <v>11</v>
+      </c>
+      <c r="G95" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>5</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C96" s="3">
-        <v>25</v>
-      </c>
-      <c r="D96" s="3">
+      <c r="C96" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D96" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F96" s="3">
-        <v>11</v>
-      </c>
-      <c r="G96" s="3">
-        <v>2</v>
-      </c>
-      <c r="H96" s="4"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="3">
-        <v>5</v>
-      </c>
-      <c r="B97" s="3" t="s">
+      <c r="E96" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F96" s="1">
+        <v>11</v>
+      </c>
+      <c r="G96" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>5</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C97" s="3">
-        <v>25</v>
-      </c>
-      <c r="D97" s="3">
+      <c r="C97" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D97" s="1">
         <v>252500000000</v>
       </c>
-      <c r="E97" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F97" s="3">
-        <v>11</v>
-      </c>
-      <c r="G97" s="3">
-        <v>2</v>
-      </c>
-      <c r="H97" s="4"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="3">
-        <v>5</v>
-      </c>
-      <c r="B98" s="3" t="s">
+      <c r="E97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" s="1">
+        <v>11</v>
+      </c>
+      <c r="G97" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>5</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C98" s="3">
-        <v>25</v>
-      </c>
-      <c r="D98" s="3">
+      <c r="C98" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D98" s="1">
         <v>500000568</v>
       </c>
-      <c r="E98" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F98" s="3">
-        <v>11</v>
-      </c>
-      <c r="G98" s="3">
-        <v>2</v>
-      </c>
-      <c r="H98" s="4"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="3">
-        <v>5</v>
-      </c>
-      <c r="B99" s="3" t="s">
+      <c r="E98" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" s="1">
+        <v>11</v>
+      </c>
+      <c r="G98" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>5</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C99" s="3">
-        <v>25</v>
-      </c>
-      <c r="D99" s="3">
+      <c r="C99" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D99" s="1">
         <v>500000000</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F99" s="3">
-        <v>11</v>
-      </c>
-      <c r="G99" s="3">
-        <v>2</v>
-      </c>
-      <c r="H99" s="4"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="3">
-        <v>5</v>
-      </c>
-      <c r="B100" s="3" t="s">
+      <c r="E99" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" s="1">
+        <v>11</v>
+      </c>
+      <c r="G99" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>5</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C100" s="3">
-        <v>25</v>
-      </c>
-      <c r="D100" s="3">
+      <c r="C100" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D100" s="1">
         <v>500026725</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F100" s="3">
-        <v>11</v>
-      </c>
-      <c r="G100" s="3">
-        <v>2</v>
-      </c>
-      <c r="H100" s="4"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="3">
-        <v>5</v>
-      </c>
-      <c r="B101" s="3" t="s">
+      <c r="E100" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F100" s="1">
+        <v>11</v>
+      </c>
+      <c r="G100" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>5</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C101" s="3">
-        <v>25</v>
-      </c>
-      <c r="D101" s="3">
+      <c r="C101" s="1">
+        <v>2525</v>
+      </c>
+      <c r="D101" s="1">
         <v>0</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F101" s="3">
-        <v>11</v>
-      </c>
-      <c r="G101" s="3">
-        <v>2</v>
-      </c>
-      <c r="H101" s="4"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E101" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="1">
+        <v>11</v>
+      </c>
+      <c r="G101" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>6</v>
       </c>
@@ -3482,7 +3335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>6</v>
       </c>
@@ -3505,7 +3358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>6</v>
       </c>
@@ -3528,7 +3381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>6</v>
       </c>
@@ -3551,7 +3404,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>6</v>
       </c>
@@ -3574,7 +3427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>6</v>
       </c>
@@ -3597,7 +3450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>6</v>
       </c>
@@ -3608,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="D108" s="1">
-        <v>3800003865</v>
+        <v>3800005375</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>9</v>
@@ -3620,7 +3473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>6</v>
       </c>
@@ -3643,7 +3496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>6</v>
       </c>
@@ -3666,7 +3519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>6</v>
       </c>
@@ -3689,7 +3542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>6</v>
       </c>
@@ -3861,7 +3714,7 @@
         <v>37</v>
       </c>
       <c r="D119" s="1">
-        <v>600000017</v>
+        <v>600000019</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>17</v>
@@ -3884,7 +3737,7 @@
         <v>37</v>
       </c>
       <c r="D120" s="1">
-        <v>600000915</v>
+        <v>600001068</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>17</v>
@@ -4068,7 +3921,7 @@
         <v>26</v>
       </c>
       <c r="D128" s="1">
-        <v>1900012386</v>
+        <v>1900015048</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>9</v>
@@ -4321,7 +4174,7 @@
         <v>26</v>
       </c>
       <c r="D139" s="1">
-        <v>700000145</v>
+        <v>700000222</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>17</v>
@@ -4344,7 +4197,7 @@
         <v>26</v>
       </c>
       <c r="D140" s="1">
-        <v>700021807</v>
+        <v>700024693</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>17</v>
@@ -4528,7 +4381,7 @@
         <v>27</v>
       </c>
       <c r="D148" s="1">
-        <v>2000010672</v>
+        <v>2000011814</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>9</v>
@@ -4804,7 +4657,7 @@
         <v>27</v>
       </c>
       <c r="D160" s="1">
-        <v>800026987</v>
+        <v>800031384</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>17</v>
@@ -4988,7 +4841,7 @@
         <v>37</v>
       </c>
       <c r="D168" s="1">
-        <v>4200004626</v>
+        <v>4200005641</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>9</v>
@@ -5448,7 +5301,7 @@
         <v>43</v>
       </c>
       <c r="D188" s="1">
-        <v>4400004249</v>
+        <v>4400007833</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>9</v>
@@ -5701,7 +5554,7 @@
         <v>43</v>
       </c>
       <c r="D199" s="1">
-        <v>1000000217</v>
+        <v>1000000458</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>17</v>
@@ -5724,7 +5577,7 @@
         <v>43</v>
       </c>
       <c r="D200" s="1">
-        <v>1000005655</v>
+        <v>1000009153</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>17</v>
@@ -5767,10 +5620,10 @@
         <v>0</v>
       </c>
       <c r="C202" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D202" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>1</v>
@@ -5790,10 +5643,10 @@
         <v>2</v>
       </c>
       <c r="C203" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D203" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>1</v>
@@ -5813,10 +5666,10 @@
         <v>3</v>
       </c>
       <c r="C204" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D204" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>1</v>
@@ -5836,10 +5689,10 @@
         <v>4</v>
       </c>
       <c r="C205" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D205" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>5</v>
@@ -5859,10 +5712,10 @@
         <v>6</v>
       </c>
       <c r="C206" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D206" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>5</v>
@@ -5882,10 +5735,10 @@
         <v>7</v>
       </c>
       <c r="C207" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D207" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>5</v>
@@ -5905,10 +5758,10 @@
         <v>8</v>
       </c>
       <c r="C208" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D208" s="1">
-        <v>4700000151</v>
+        <v>4700000617</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>9</v>
@@ -5928,10 +5781,10 @@
         <v>10</v>
       </c>
       <c r="C209" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D209" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>1</v>
@@ -5951,10 +5804,10 @@
         <v>11</v>
       </c>
       <c r="C210" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D210" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>1</v>
@@ -5974,10 +5827,10 @@
         <v>12</v>
       </c>
       <c r="C211" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D211" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>1</v>
@@ -5997,10 +5850,10 @@
         <v>13</v>
       </c>
       <c r="C212" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D212" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>5</v>
@@ -6020,10 +5873,10 @@
         <v>14</v>
       </c>
       <c r="C213" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D213" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>5</v>
@@ -6043,10 +5896,10 @@
         <v>15</v>
       </c>
       <c r="C214" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D214" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>5</v>
@@ -6066,7 +5919,7 @@
         <v>16</v>
       </c>
       <c r="C215" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D215" s="1">
         <v>1100000000</v>
@@ -6089,10 +5942,10 @@
         <v>18</v>
       </c>
       <c r="C216" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D216" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>17</v>
@@ -6112,10 +5965,10 @@
         <v>19</v>
       </c>
       <c r="C217" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D217" s="1">
-        <v>4600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>17</v>
@@ -6135,7 +5988,7 @@
         <v>20</v>
       </c>
       <c r="C218" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D218" s="1">
         <v>1100000000</v>
@@ -6158,10 +6011,10 @@
         <v>21</v>
       </c>
       <c r="C219" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D219" s="1">
-        <v>1100000000</v>
+        <v>1100000002</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>17</v>
@@ -6181,10 +6034,10 @@
         <v>22</v>
       </c>
       <c r="C220" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D220" s="1">
-        <v>1100000006</v>
+        <v>1100000009</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>17</v>
@@ -6204,7 +6057,7 @@
         <v>23</v>
       </c>
       <c r="C221" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D221" s="1">
         <v>1100000000</v>
@@ -6219,8 +6072,467 @@
         <v>2</v>
       </c>
     </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="1">
+        <v>12</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C222" s="1">
+        <v>50</v>
+      </c>
+      <c r="D222" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F222" s="1">
+        <v>11</v>
+      </c>
+      <c r="G222" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="1">
+        <v>12</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C223" s="1">
+        <v>50</v>
+      </c>
+      <c r="D223" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F223" s="1">
+        <v>11</v>
+      </c>
+      <c r="G223" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="1">
+        <v>12</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C224" s="1">
+        <v>50</v>
+      </c>
+      <c r="D224" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F224" s="1">
+        <v>11</v>
+      </c>
+      <c r="G224" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" s="1">
+        <v>12</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C225" s="1">
+        <v>50</v>
+      </c>
+      <c r="D225" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F225" s="1">
+        <v>11</v>
+      </c>
+      <c r="G225" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" s="1">
+        <v>12</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C226" s="1">
+        <v>50</v>
+      </c>
+      <c r="D226" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F226" s="1">
+        <v>11</v>
+      </c>
+      <c r="G226" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" s="1">
+        <v>12</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C227" s="1">
+        <v>50</v>
+      </c>
+      <c r="D227" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F227" s="1">
+        <v>11</v>
+      </c>
+      <c r="G227" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="1">
+        <v>12</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C228" s="1">
+        <v>50</v>
+      </c>
+      <c r="D228" s="1">
+        <v>5100000344</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F228" s="1">
+        <v>11</v>
+      </c>
+      <c r="G228" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="1">
+        <v>12</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C229" s="1">
+        <v>50</v>
+      </c>
+      <c r="D229" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F229" s="1">
+        <v>11</v>
+      </c>
+      <c r="G229" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="1">
+        <v>12</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C230" s="1">
+        <v>50</v>
+      </c>
+      <c r="D230" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F230" s="1">
+        <v>11</v>
+      </c>
+      <c r="G230" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
+        <v>12</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C231" s="1">
+        <v>50</v>
+      </c>
+      <c r="D231" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F231" s="1">
+        <v>11</v>
+      </c>
+      <c r="G231" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
+        <v>12</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C232" s="1">
+        <v>50</v>
+      </c>
+      <c r="D232" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F232" s="1">
+        <v>11</v>
+      </c>
+      <c r="G232" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
+        <v>12</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C233" s="1">
+        <v>50</v>
+      </c>
+      <c r="D233" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F233" s="1">
+        <v>11</v>
+      </c>
+      <c r="G233" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
+        <v>12</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C234" s="1">
+        <v>50</v>
+      </c>
+      <c r="D234" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F234" s="1">
+        <v>11</v>
+      </c>
+      <c r="G234" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="1">
+        <v>12</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C235" s="1">
+        <v>50</v>
+      </c>
+      <c r="D235" s="1">
+        <v>1200000000</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F235" s="1">
+        <v>11</v>
+      </c>
+      <c r="G235" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" s="1">
+        <v>12</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C236" s="1">
+        <v>50</v>
+      </c>
+      <c r="D236" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F236" s="1">
+        <v>11</v>
+      </c>
+      <c r="G236" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="1">
+        <v>12</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C237" s="1">
+        <v>50</v>
+      </c>
+      <c r="D237" s="1">
+        <v>5000000000</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F237" s="1">
+        <v>11</v>
+      </c>
+      <c r="G237" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" s="1">
+        <v>12</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C238" s="1">
+        <v>50</v>
+      </c>
+      <c r="D238" s="1">
+        <v>1200000000</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F238" s="1">
+        <v>11</v>
+      </c>
+      <c r="G238" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" s="1">
+        <v>12</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C239" s="1">
+        <v>50</v>
+      </c>
+      <c r="D239" s="1">
+        <v>1200000671</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F239" s="1">
+        <v>11</v>
+      </c>
+      <c r="G239" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" s="1">
+        <v>12</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C240" s="1">
+        <v>50</v>
+      </c>
+      <c r="D240" s="1">
+        <v>1200001519</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F240" s="1">
+        <v>11</v>
+      </c>
+      <c r="G240" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="1">
+        <v>12</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C241" s="1">
+        <v>50</v>
+      </c>
+      <c r="D241" s="1">
+        <v>1200000000</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F241" s="1">
+        <v>11</v>
+      </c>
+      <c r="G241" s="1">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G221" xr:uid="{566DD4C6-E472-4C8E-BB58-53751169563F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/neumatic/data_load/numeracion.xlsx
+++ b/neumatic/data_load/numeracion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT_NEUMATIC_PGS\neumatic\data_load\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E23CAF-0186-4F3A-A586-D1F2018EFFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7891855F-7154-49ED-B058-A58074C5F68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{82F2B0B3-B52D-4681-8559-E900541B57A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{37978315-4162-4761-92E3-1BFA22521079}"/>
   </bookViews>
   <sheets>
     <sheet name="numeracion" sheetId="1" r:id="rId1"/>
@@ -100,9 +100,6 @@
     <t>sucursal</t>
   </si>
   <si>
-    <t>comprobante</t>
-  </si>
-  <si>
     <t>puntoventa</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
   </si>
   <si>
     <t>copias</t>
+  </si>
+  <si>
+    <t>comprobante</t>
   </si>
 </sst>
 </file>
@@ -976,7 +976,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0FFF690-0665-4CFC-8CA8-412D52A4D68A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907D11B6-3AA3-4972-9457-2B19D1A7474E}">
   <dimension ref="A1:G241"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -990,26 +990,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1161,7 +1161,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="1">
-        <v>3300016062</v>
+        <v>3300016136</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>9</v>
@@ -1414,7 +1414,7 @@
         <v>21</v>
       </c>
       <c r="D19" s="1">
-        <v>100001063</v>
+        <v>100001072</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>17</v>
@@ -1437,7 +1437,7 @@
         <v>21</v>
       </c>
       <c r="D20" s="1">
-        <v>100155366</v>
+        <v>100155543</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>17</v>
@@ -1460,7 +1460,7 @@
         <v>21</v>
       </c>
       <c r="D21" s="1">
-        <v>1900000053</v>
+        <v>38000002583</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>17</v>
@@ -1621,7 +1621,7 @@
         <v>22</v>
       </c>
       <c r="D28" s="1">
-        <v>3400003565</v>
+        <v>3400003572</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>9</v>
@@ -1851,7 +1851,7 @@
         <v>22</v>
       </c>
       <c r="D38" s="1">
-        <v>200001014</v>
+        <v>200001025</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>17</v>
@@ -1874,7 +1874,7 @@
         <v>22</v>
       </c>
       <c r="D39" s="1">
-        <v>200000749</v>
+        <v>200000759</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>17</v>
@@ -1897,7 +1897,7 @@
         <v>22</v>
       </c>
       <c r="D40" s="1">
-        <v>200161073</v>
+        <v>200161175</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>17</v>
@@ -2081,7 +2081,7 @@
         <v>23</v>
       </c>
       <c r="D48" s="1">
-        <v>3500010844</v>
+        <v>3500010866</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>9</v>
@@ -2311,7 +2311,7 @@
         <v>23</v>
       </c>
       <c r="D58" s="1">
-        <v>300001290</v>
+        <v>300001292</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>17</v>
@@ -2334,7 +2334,7 @@
         <v>23</v>
       </c>
       <c r="D59" s="1">
-        <v>300002616</v>
+        <v>300002629</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>17</v>
@@ -2357,7 +2357,7 @@
         <v>23</v>
       </c>
       <c r="D60" s="1">
-        <v>300061159</v>
+        <v>300061205</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>17</v>
@@ -2541,7 +2541,7 @@
         <v>24</v>
       </c>
       <c r="D68" s="1">
-        <v>3600014085</v>
+        <v>3600014112</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>9</v>
@@ -2817,7 +2817,7 @@
         <v>24</v>
       </c>
       <c r="D80" s="1">
-        <v>400061367</v>
+        <v>400061418</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>17</v>
@@ -3737,7 +3737,7 @@
         <v>37</v>
       </c>
       <c r="D120" s="1">
-        <v>600001068</v>
+        <v>600001070</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>17</v>
@@ -3921,7 +3921,7 @@
         <v>26</v>
       </c>
       <c r="D128" s="1">
-        <v>1900015048</v>
+        <v>1900015090</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>9</v>
@@ -4197,7 +4197,7 @@
         <v>26</v>
       </c>
       <c r="D140" s="1">
-        <v>700024693</v>
+        <v>700024738</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>17</v>
@@ -4381,7 +4381,7 @@
         <v>27</v>
       </c>
       <c r="D148" s="1">
-        <v>2000011814</v>
+        <v>2000011824</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>9</v>
@@ -4657,7 +4657,7 @@
         <v>27</v>
       </c>
       <c r="D160" s="1">
-        <v>800031384</v>
+        <v>800031473</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>17</v>
@@ -5301,7 +5301,7 @@
         <v>43</v>
       </c>
       <c r="D188" s="1">
-        <v>4400007833</v>
+        <v>4400007890</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>9</v>
@@ -5554,7 +5554,7 @@
         <v>43</v>
       </c>
       <c r="D199" s="1">
-        <v>1000000458</v>
+        <v>1000000463</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>17</v>
@@ -5577,7 +5577,7 @@
         <v>43</v>
       </c>
       <c r="D200" s="1">
-        <v>1000009153</v>
+        <v>1000009203</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>17</v>
@@ -5761,7 +5761,7 @@
         <v>52</v>
       </c>
       <c r="D208" s="1">
-        <v>4700000617</v>
+        <v>4700000622</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>9</v>
@@ -6221,7 +6221,7 @@
         <v>50</v>
       </c>
       <c r="D228" s="1">
-        <v>5100000344</v>
+        <v>5100000349</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>9</v>
@@ -6474,7 +6474,7 @@
         <v>50</v>
       </c>
       <c r="D239" s="1">
-        <v>1200000671</v>
+        <v>1200000691</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>17</v>
@@ -6497,7 +6497,7 @@
         <v>50</v>
       </c>
       <c r="D240" s="1">
-        <v>1200001519</v>
+        <v>1200001548</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>17</v>
